--- a/utimaco/2026II/utimaco-admin-api/data/test_data.xlsx
+++ b/utimaco/2026II/utimaco-admin-api/data/test_data.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Section 8 FileServer 地址(待确认，需替换为实际地址)</t>
+          <t>Section 8 FileServer 地址(待替换为实际地址)</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Section 9 租户密评 VSM 地址(待确认，需替换为实际地址)</t>
+          <t>Section 9 租户密评 VSM 地址(待替换为实际地址)</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,194 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>异步回调 mock 地址</t>
+          <t>异步操作回调 mock 地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>uploadUrl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>http://10.10.1.207:8080/upload</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>configCHSMUploadAddress 影像上传地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>alarmUrl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>http://10.10.1.100:9090/alarm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>configCHSMAlarmAddress 告警地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>monitoringUrl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>http://10.10.1.100:9090/monitoring</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>configCHSMAlarmAddress 监控地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>logServerUrl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>http://10.10.1.100:9200/logs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>configSyslogAddr logserver 地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>chsmImageUrl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>http://192.168.0.1/chsm_image.zip</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>importCHSM 影像文件URL(待替换为真实文件服务器)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>chsmPackUrl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>http://192.168.0.1/chsm_pack.bin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>upgradeCHSM 升级包URL(待替换为真实文件服务器)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>chsmBackupUrl</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>http://192.168.0.1/chsm_backup.dat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>restoreCHSM 备份文件URL(待替换为真实文件服务器)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vsmImageUrl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>http://192.168.0.1/vsm_image.zip</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>importVSM 影像文件URL(待替换为真实文件服务器)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>vsmPackUrl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>http://192.168.0.1/vsm_pack.bin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>upgradeVSM 升级包URL(待替换为真实文件服务器)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>signBase64</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER_SIGN_BASE64</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>import/restore 签名值(BASE64编码，待替换为真实签名)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>signHex</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER_SIGN_HEX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>upgrade 签名值(HEX编码，待替换为真实签名)</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7217,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "url": "http://10.10.1.207:8080/upload"}</t>
+          <t>{"requestId": "uuid", "url": "${env.uploadUrl}"}</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -7130,7 +7317,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{"requestId": "", "url": "http://10.10.1.207:8080/upload"}</t>
+          <t>{"requestId": "", "url": "${env.uploadUrl}"}</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -7175,7 +7362,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>{"url": "http://10.10.1.207:8080/upload"}</t>
+          <t>{"url": "${env.uploadUrl}"}</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -7360,7 +7547,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "logServerType": "logserver", "logServerAddress": "http://10.10.1.100:9200/logs"}</t>
+          <t>{"requestId": "uuid", "logServerType": "logserver", "logServerAddress": "${env.logServerUrl}"}</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -7685,7 +7872,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "url": "http://10.10.1.100:9090/alarm", "monitoringUrl": "http://10.10.1.100:9090/monitoring"}</t>
+          <t>{"requestId": "uuid", "url": "${env.alarmUrl}", "monitoringUrl": "${env.monitoringUrl}"}</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -7735,7 +7922,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "url": "http://10.10.1.100:9090/alarm"}</t>
+          <t>{"requestId": "uuid", "url": "${env.alarmUrl}"}</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -7785,7 +7972,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>{"requestId": "", "url": "http://10.10.1.100:9090/alarm"}</t>
+          <t>{"requestId": "", "url": "${env.alarmUrl}"}</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -7830,7 +8017,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>{"url": "http://10.10.1.100:9090/alarm"}</t>
+          <t>{"url": "${env.alarmUrl}"}</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -8525,7 +8712,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "export", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "export", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -8625,7 +8812,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "export", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "export", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -8670,7 +8857,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>{"oprType": "export", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"oprType": "export", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -8715,7 +8902,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -8805,7 +8992,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "http://192.168.0.1/chsm_image.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "${env.chsmImageUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -8855,7 +9042,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "http://192.168.99.99/no_exist.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "http://192.168.99.99/no_exist.zip", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -8905,7 +9092,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "http://192.168.0.1/chsm_image.zip", "alg": "RSAWithSHA256", "sign": "TAMPERED_SIGN_VALUE", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "${env.chsmImageUrl}", "alg": "RSAWithSHA256", "sign": "TAMPERED_SIGN_VALUE", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -8955,7 +9142,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "http://192.168.0.1/chsm_image.zip", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "${env.chsmImageUrl}", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -9005,7 +9192,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "import", "imageUrl": "http://192.168.0.1/chsm_image.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "import", "imageUrl": "${env.chsmImageUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -9050,7 +9237,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>{"oprType": "import", "imageUrl": "http://192.168.0.1/chsm_image.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"oprType": "import", "imageUrl": "${env.chsmImageUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -9095,7 +9282,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -9140,7 +9327,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "http://192.168.0.1/chsm_image.zip", "alg": "RSAWithSHA256", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "${env.chsmImageUrl}", "alg": "RSAWithSHA256", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -9185,7 +9372,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "http://192.168.0.1/chsm_image.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "${env.chsmImageUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}"}</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -9230,7 +9417,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "imageUrl": "http://192.168.0.1/chsm_image.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "imageUrl": "${env.chsmImageUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -9275,7 +9462,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "http://192.168.0.1/chsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "${env.chsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -9325,7 +9512,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "http://192.168.99.99/no_exist.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "http://192.168.99.99/no_exist.bin", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -9375,7 +9562,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "http://192.168.0.1/chsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "${env.chsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -9420,7 +9607,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>{"oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "http://192.168.0.1/chsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "${env.chsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -9465,7 +9652,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "packUrl": "http://192.168.0.1/chsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "packUrl": "${env.chsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -9510,7 +9697,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -9555,7 +9742,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "http://192.168.0.1/chsm_pack.bin", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "${env.chsmPackUrl}", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -9600,7 +9787,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "http://192.168.0.1/chsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "2.0.1", "packUrl": "${env.chsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}"}</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -9645,7 +9832,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "restart", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "restart", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -9695,7 +9882,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "restart", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "restart", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -9740,7 +9927,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>{"oprType": "restart", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"oprType": "restart", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -9830,7 +10017,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -9875,7 +10062,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "backup", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "backup", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -9925,7 +10112,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "backup", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "backup", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -9970,7 +10157,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>{"oprType": "backup", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"oprType": "backup", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H102" t="n">
@@ -10060,7 +10247,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -10105,7 +10292,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "restore", "backupUrl": "http://192.168.0.1/chsm_backup.dat", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "restore", "backupUrl": "${env.chsmBackupUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -10155,7 +10342,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "restore", "backupUrl": "http://192.168.0.1/chsm_backup.dat", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "restore", "backupUrl": "${env.chsmBackupUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -10200,7 +10387,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>{"oprType": "restore", "backupUrl": "http://192.168.0.1/chsm_backup.dat", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"oprType": "restore", "backupUrl": "${env.chsmBackupUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H107" t="n">
@@ -10245,7 +10432,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "restore", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "restore", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -10290,7 +10477,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "restore", "backupUrl": "http://192.168.0.1/chsm_backup.dat", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "restore", "backupUrl": "${env.chsmBackupUrl}", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -10335,7 +10522,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "restore", "backupUrl": "http://192.168.0.1/chsm_backup.dat", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64"}</t>
+          <t>{"requestId": "uuid", "oprType": "restore", "backupUrl": "${env.chsmBackupUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}"}</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -11575,7 +11762,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "export", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "export", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -11638,7 +11825,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "export", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "export", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -11696,7 +11883,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "export", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "export", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -11812,7 +11999,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "vsmId": "${vsmId}", "imageUrl": "http://192.168.0.1/vsm_image.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "vsmId": "${vsmId}", "imageUrl": "${env.vsmImageUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -11875,7 +12062,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "import", "vsmId": "${vsmId}", "imageUrl": "http://192.168.0.1/vsm_image.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "import", "vsmId": "${vsmId}", "imageUrl": "${env.vsmImageUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11933,7 +12120,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "http://192.168.0.1/vsm_image.zip", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "imageUrl": "${env.vsmImageUrl}", "alg": "RSAWithSHA256", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -11991,7 +12178,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "import", "vsmId": "${vsmId}", "imageUrl": "http://192.168.0.1/vsm_image.zip", "sign": "PLACEHOLDER_SIGN_BASE64", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "import", "vsmId": "${vsmId}", "imageUrl": "${env.vsmImageUrl}", "sign": "${env.signBase64}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -12049,7 +12236,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "start", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "start", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -12112,7 +12299,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "start", "vsmId": "non_existent_id", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "start", "vsmId": "non_existent_id", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -12175,7 +12362,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "start", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "start", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -12233,7 +12420,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "start", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "start", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H142" t="n">
@@ -12291,7 +12478,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H143" t="n">
@@ -12349,7 +12536,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "stop", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "stop", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -12412,7 +12599,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "stop", "vsmId": "non_existent_id", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "stop", "vsmId": "non_existent_id", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H145" t="n">
@@ -12475,7 +12662,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "stop", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "stop", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H146" t="n">
@@ -12533,7 +12720,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "stop", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "stop", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -12591,7 +12778,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "restart", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "restart", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H148" t="n">
@@ -12654,7 +12841,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "restart", "vsmId": "non_existent_id", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "restart", "vsmId": "non_existent_id", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H149" t="n">
@@ -12717,7 +12904,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "restart", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "restart", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H150" t="n">
@@ -12775,7 +12962,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "restart", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "restart", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -12833,7 +13020,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "reset", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "reset", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -12896,7 +13083,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "reset", "vsmId": "non_existent_id", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "reset", "vsmId": "non_existent_id", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H153" t="n">
@@ -12959,7 +13146,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "reset", "vsmId": "${vsmId}", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "reset", "vsmId": "${vsmId}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H154" t="n">
@@ -13017,7 +13204,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "reset", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "reset", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H155" t="n">
@@ -13075,7 +13262,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "vsmId": "${vsmId}", "packVersion": "1.5.0", "packUrl": "http://192.168.0.1/vsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "vsmId": "${vsmId}", "packVersion": "1.5.0", "packUrl": "${env.vsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H156" t="n">
@@ -13138,7 +13325,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>{"requestId": "", "oprType": "upgrade", "vsmId": "${vsmId}", "packVersion": "1.5.0", "packUrl": "http://192.168.0.1/vsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "", "oprType": "upgrade", "vsmId": "${vsmId}", "packVersion": "1.5.0", "packUrl": "${env.vsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H157" t="n">
@@ -13196,7 +13383,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "1.5.0", "packUrl": "http://192.168.0.1/vsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "packVersion": "1.5.0", "packUrl": "${env.vsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H158" t="n">
@@ -13254,7 +13441,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "vsmId": "${vsmId}", "packUrl": "http://192.168.0.1/vsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX", "callbackUrl": "http://10.10.1.207:8000/callback"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "vsmId": "${vsmId}", "packUrl": "${env.vsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}", "callbackUrl": "${env.callbackUrl}"}</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -13312,7 +13499,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>{"requestId": "uuid", "oprType": "upgrade", "vsmId": "${vsmId}", "packVersion": "1.5.0", "packUrl": "http://192.168.0.1/vsm_pack.bin", "alg": "RSAWithSHA256", "sign": "PLACEHOLDER_SIGN_HEX"}</t>
+          <t>{"requestId": "uuid", "oprType": "upgrade", "vsmId": "${vsmId}", "packVersion": "1.5.0", "packUrl": "${env.vsmPackUrl}", "alg": "RSAWithSHA256", "sign": "${env.signHex}"}</t>
         </is>
       </c>
       <c r="H160" t="n">
